--- a/output/pdf_financials_xlsx/CAND.H.xlsx
+++ b/output/pdf_financials_xlsx/CAND.H.xlsx
@@ -1171,10 +1171,10 @@
         <v>-4.386</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>14.246</v>
+        <v>-14.246</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>1.875</v>
+        <v>-1.875</v>
       </c>
     </row>
     <row r="17">
@@ -1423,10 +1423,10 @@
         <v>-4.386</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>14.246</v>
+        <v>-14.246</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>1.875</v>
+        <v>-1.875</v>
       </c>
     </row>
     <row r="21">
@@ -1570,10 +1570,10 @@
         <v>-4.386</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>14.246</v>
+        <v>-14.246</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>1.875</v>
+        <v>-1.875</v>
       </c>
     </row>
     <row r="24">
@@ -1725,7 +1725,7 @@
         <v>146.2</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>142.46</v>
+        <v>-142.46</v>
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
@@ -1776,10 +1776,10 @@
         <v>-4.386</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>14.246</v>
+        <v>-14.246</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>1.875</v>
+        <v>-1.875</v>
       </c>
     </row>
     <row r="28">
@@ -1874,10 +1874,10 @@
         <v>-4.386</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>14.246</v>
+        <v>-14.246</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>1.875</v>
+        <v>-1.875</v>
       </c>
     </row>
     <row r="30">
@@ -2000,10 +2000,10 @@
         <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -5039,31 +5039,31 @@
         <v>0</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.145</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>3.195</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.955</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>4.715</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>2.937</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>10.149</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>10.467</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>13.442</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>14.423</v>
       </c>
       <c r="O92" s="3" t="n">
         <v>0</v>
@@ -10442,7 +10442,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
@@ -11422,7 +11426,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>-</t>
@@ -34324,10 +34332,10 @@
         </is>
       </c>
       <c r="Q319" s="5" t="n">
-        <v>14.246</v>
+        <v>-14.246</v>
       </c>
       <c r="R319" s="5" t="n">
-        <v>1.875</v>
+        <v>-1.875</v>
       </c>
     </row>
     <row r="320">
@@ -34496,10 +34504,10 @@
         </is>
       </c>
       <c r="Q321" s="5" t="n">
-        <v>13.195</v>
+        <v>-13.195</v>
       </c>
       <c r="R321" s="5" t="n">
-        <v>1.647</v>
+        <v>-1.647</v>
       </c>
     </row>
     <row r="322">
@@ -53319,7 +53327,7 @@
         <v>-0.017782</v>
       </c>
       <c r="F544" s="5" t="n">
-        <v>0.163752</v>
+        <v>-0.163752</v>
       </c>
       <c r="G544" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/CAND.H.xlsx
+++ b/output/pdf_financials_xlsx/CAND.H.xlsx
@@ -2097,13 +2097,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.073334</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.143401</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.054145</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>2.306361</v>
@@ -2133,10 +2133,10 @@
         <v>1.089</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.282</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="35">
@@ -2195,13 +2195,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.073334</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.143401</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.054145</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>2.306361</v>
@@ -2231,10 +2231,10 @@
         <v>1.089</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.282</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="37">
@@ -2819,10 +2819,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.324</v>
+        <v>0.042</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>4.623</v>
+        <v>4.615</v>
       </c>
     </row>
     <row r="49">
@@ -7410,7 +7410,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -9228,7 +9228,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -15728,7 +15728,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E102" s="5" t="n">

--- a/output/pdf_financials_xlsx/CAND.H.xlsx
+++ b/output/pdf_financials_xlsx/CAND.H.xlsx
@@ -5429,16 +5429,16 @@
         <v>0</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.006555</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>0.005057</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>-0.001264</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0</v>
+        <v>-0.003961</v>
       </c>
       <c r="G101" s="3" t="n">
         <v>0</v>
@@ -5674,16 +5674,16 @@
         <v>-0.000212</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.011536</v>
+        <v>0.004981</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>-0.003311</v>
+        <v>0.001746</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0.01707</v>
+        <v>0.015806</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0.054845</v>
+        <v>0.050884</v>
       </c>
       <c r="G106" s="3" t="n">
         <v>0</v>
@@ -5900,13 +5900,13 @@
         <v>0</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>0</v>
+        <v>0.064</v>
       </c>
       <c r="N110" s="3" t="n">
-        <v>0</v>
+        <v>0.073</v>
       </c>
       <c r="O110" s="3" t="n">
-        <v>0</v>
+        <v>0.08500000000000001</v>
       </c>
     </row>
     <row r="111">
@@ -17574,7 +17574,11 @@
           <t>Accretion 8</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
           <t>-</t>
@@ -18950,7 +18954,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E140" t="inlineStr">
         <is>
           <t>-</t>
@@ -20252,7 +20260,11 @@
           <t>Proceeds from private placement 9</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E155" t="inlineStr">
         <is>
           <t>-</t>
@@ -29062,7 +29074,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr"/>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E258" t="inlineStr">
         <is>
           <t>-</t>
@@ -32404,7 +32420,11 @@
           <t>HST receivable</t>
         </is>
       </c>
-      <c r="D297" t="inlineStr"/>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E297" t="inlineStr">
         <is>
           <t>-</t>
